--- a/assets/Tableau_synthèse_E4 Septembre (version 1) (2).xlsx
+++ b/assets/Tableau_synthèse_E4 Septembre (version 1) (2).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\BTS SIO 2éme Année\Support et mise à dispo SI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16E1C6CE-221D-430E-B492-D64B3C21E88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32595F0D-27E6-4788-AEC6-527B3E6DFF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{153D34F4-B3E1-4E5F-A890-6C4EE2AE512C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="648" firstSheet="1" activeTab="2" xr2:uid="{153D34F4-B3E1-4E5F-A890-6C4EE2AE512C}"/>
   </bookViews>
   <sheets>
     <sheet name="Exemple" sheetId="1" r:id="rId1"/>
@@ -34,12 +34,11 @@
     <sheet name="19. Clément" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="81">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -156,34 +155,19 @@
     <t>07/11/24 - 30/11/24</t>
   </si>
   <si>
-    <t>Clone Discord (php / sql / bootstrap)</t>
-  </si>
-  <si>
     <t>25/03/25 - 19/05/25</t>
-  </si>
-  <si>
-    <t>Projet application Java pour une billeterie</t>
   </si>
   <si>
     <t>01/09/25 - 15/12/25</t>
   </si>
   <si>
-    <t>Mini jeu java</t>
-  </si>
-  <si>
     <t>15/12/25 - 15/02/26</t>
-  </si>
-  <si>
-    <t>TP wireframe html et css</t>
   </si>
   <si>
     <t>22/09/25 - 29/09/25</t>
   </si>
   <si>
     <t>15/01/25 - 29/08/25</t>
-  </si>
-  <si>
-    <t>Module de formation JavaScript / TypeScript</t>
   </si>
   <si>
     <t>NOM et prénom : MOULIN Dylan</t>
@@ -288,10 +272,48 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Site vitrine html et css                                                                                     </t>
+    <t xml:space="preserve">Réalisations en milieu professionnel en cours de première année et deuxiéme année </t>
   </si>
   <si>
-    <t xml:space="preserve">Réalisations en milieu professionnel en cours de première année et deuxiéme année </t>
+    <t>Adresse URL du portfolio : https://ashvin-portfolio.dev/</t>
+  </si>
+  <si>
+    <t>07/11/25 - 19/12/25</t>
+  </si>
+  <si>
+    <t>Application web "QuizNova" interactive pour démontrer la maîtrise d’Angular, TypeScript et JavaScript.
+(Codesource, Application, CR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site vitrine html et css
+(codesource, Site, CR)                                                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Module de formation JavaScript / TypeScript  
+(CR)                           </t>
+  </si>
+  <si>
+    <t>Mini jeu java ( Bataille Navale ) 
+(Codesource, Application, CR)</t>
+  </si>
+  <si>
+    <t>TP wireframe html et css
+(Codesource, Site, CR)</t>
+  </si>
+  <si>
+    <t>Projet application Java pour une billeterie
+(Codesource, Application, CR)</t>
+  </si>
+  <si>
+    <t>Clone Discord (php / sql / bootstrap)
+(Codesource, Application, CR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                     Projet Bibliothéque Laravel
+                                   (Codesource, Application, CR)</t>
+  </si>
+  <si>
+    <t>16/02/26 - 16/03/26</t>
   </si>
 </sst>
 </file>
@@ -537,13 +559,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.499984740745262"/>
+        <fgColor theme="9"/>
         <bgColor rgb="FF4A86E8"/>
       </patternFill>
     </fill>
@@ -724,13 +746,13 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -745,10 +767,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1112,30 +1134,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -1342,16 +1364,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -1424,16 +1446,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -2504,30 +2526,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -2635,7 +2657,7 @@
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
@@ -2647,7 +2669,7 @@
     </row>
     <row r="10" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="9"/>
@@ -2659,7 +2681,7 @@
     </row>
     <row r="11" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="9"/>
@@ -2671,7 +2693,7 @@
     </row>
     <row r="12" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="9"/>
@@ -2683,7 +2705,7 @@
     </row>
     <row r="13" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="9"/>
@@ -2695,7 +2717,7 @@
     </row>
     <row r="14" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="9"/>
@@ -2746,20 +2768,20 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="9"/>
@@ -2771,7 +2793,7 @@
     </row>
     <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="12"/>
@@ -2832,16 +2854,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -3912,30 +3934,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -4142,16 +4164,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -4224,16 +4246,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -5304,30 +5326,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -5534,16 +5556,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -5616,16 +5638,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -6696,30 +6718,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -6827,7 +6849,7 @@
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="8"/>
@@ -6928,16 +6950,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -7010,16 +7032,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -8093,30 +8115,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -8323,16 +8345,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -8405,16 +8427,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -9485,34 +9507,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -9539,7 +9561,7 @@
         <v>7</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -9715,16 +9737,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -9797,16 +9819,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -10877,30 +10899,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -11107,16 +11129,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -11189,16 +11211,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -12269,30 +12291,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -12499,16 +12521,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -12581,16 +12603,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -13661,30 +13683,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -13891,16 +13913,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -13973,16 +13995,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -15053,30 +15075,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -15283,16 +15305,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -15365,16 +15387,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -16445,30 +16467,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -16675,16 +16697,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -16757,16 +16779,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -17837,30 +17859,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -17896,7 +17918,7 @@
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -17968,77 +17990,81 @@
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="9"/>
-      <c r="H9" s="29"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="13" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="29"/>
+      <c r="H13" s="22"/>
     </row>
     <row r="14" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>80</v>
+      </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -18076,54 +18102,58 @@
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
+      <c r="A18" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
     </row>
     <row r="19" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
     </row>
     <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
     </row>
     <row r="22" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
@@ -18164,7 +18194,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -19143,17 +19173,17 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="1.1437499999999998" bottom="1.1437499999999998" header="0.75" footer="0.75"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -19173,34 +19203,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -19227,7 +19257,7 @@
         <v>7</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -19304,10 +19334,10 @@
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
@@ -19318,10 +19348,10 @@
     </row>
     <row r="10" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -19411,23 +19441,23 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="13"/>
@@ -19438,10 +19468,10 @@
     </row>
     <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="13"/>
@@ -19501,23 +19531,23 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="13"/>
@@ -19528,10 +19558,10 @@
     </row>
     <row r="29" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C29" s="15"/>
       <c r="D29" s="13"/>
@@ -20585,30 +20615,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -20815,16 +20845,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -20897,16 +20927,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -21977,34 +22007,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B3" s="24"/>
       <c r="C3" s="24"/>
@@ -22018,7 +22048,7 @@
     </row>
     <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
@@ -22031,7 +22061,7 @@
         <v>7</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
@@ -22108,10 +22138,10 @@
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
@@ -22122,7 +22152,7 @@
     </row>
     <row r="10" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="9"/>
@@ -22134,7 +22164,7 @@
     </row>
     <row r="11" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="9"/>
@@ -22146,7 +22176,7 @@
     </row>
     <row r="12" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="13"/>
@@ -22158,7 +22188,7 @@
     </row>
     <row r="13" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="9"/>
@@ -22219,20 +22249,20 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B20" s="17">
         <v>45536</v>
@@ -22304,16 +22334,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -23384,30 +23414,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -23614,16 +23644,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -23696,16 +23726,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -24776,30 +24806,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -25006,16 +25036,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -25088,16 +25118,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -26168,30 +26198,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -26398,16 +26428,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -26480,16 +26510,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>

--- a/assets/Tableau_synthèse_E4 Septembre (version 1) (2).xlsx
+++ b/assets/Tableau_synthèse_E4 Septembre (version 1) (2).xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\BTS SIO 2éme Année\Support et mise à dispo SI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data\BTS SIO 2éme Année\Support et mise à dispo SI\portfolio Ashvin\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32595F0D-27E6-4788-AEC6-527B3E6DFF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD4E59CC-203A-446D-87F7-2502C136C786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="648" firstSheet="1" activeTab="2" xr2:uid="{153D34F4-B3E1-4E5F-A890-6C4EE2AE512C}"/>
   </bookViews>
@@ -490,7 +490,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -567,6 +567,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor rgb="FF4A86E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -688,7 +694,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -752,11 +758,14 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -767,10 +776,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1134,18 +1143,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
@@ -1204,10 +1213,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1230,8 +1239,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -1252,16 +1261,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -1364,16 +1373,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -1446,16 +1455,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -2526,30 +2535,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -2596,10 +2605,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -2622,8 +2631,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -2644,16 +2653,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
@@ -2768,16 +2777,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
@@ -2854,16 +2863,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -3934,30 +3943,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -4004,10 +4013,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -4030,8 +4039,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -4052,16 +4061,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -4164,16 +4173,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -4246,16 +4255,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -5326,30 +5335,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -5396,10 +5405,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -5422,8 +5431,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -5444,16 +5453,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -5556,16 +5565,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -5638,16 +5647,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -6718,30 +6727,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -6788,10 +6797,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -6814,8 +6823,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -6836,16 +6845,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
@@ -6950,16 +6959,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -7032,16 +7041,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -8115,30 +8124,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -8185,10 +8194,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -8211,8 +8220,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -8233,16 +8242,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -8345,16 +8354,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -8427,16 +8436,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -9507,30 +9516,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -9577,10 +9586,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -9603,8 +9612,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -9625,16 +9634,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -9737,16 +9746,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -9819,16 +9828,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -10899,30 +10908,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -10969,10 +10978,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -10995,8 +11004,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -11017,16 +11026,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -11129,16 +11138,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -11211,16 +11220,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -12291,30 +12300,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -12361,10 +12370,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -12387,8 +12396,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -12409,16 +12418,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -12521,16 +12530,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -12603,16 +12612,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -13683,30 +13692,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -13753,10 +13762,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -13779,8 +13788,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -13801,16 +13810,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -13913,16 +13922,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -13995,16 +14004,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -15075,30 +15084,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -15145,10 +15154,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -15171,8 +15180,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -15193,16 +15202,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -15305,16 +15314,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -15387,16 +15396,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -16467,30 +16476,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -16537,10 +16546,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -16563,8 +16572,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -16585,16 +16594,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -16697,16 +16706,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -16779,16 +16788,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -17859,30 +17868,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -17929,10 +17938,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -17955,8 +17964,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -17977,16 +17986,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
@@ -18010,7 +18019,7 @@
         <v>32</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
@@ -18023,7 +18032,7 @@
       <c r="B11" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="9"/>
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
@@ -18037,7 +18046,7 @@
       <c r="B12" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="9"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="22"/>
@@ -18065,11 +18074,12 @@
       <c r="B14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="9"/>
+      <c r="C14" s="30"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
     </row>
     <row r="15" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
@@ -18102,16 +18112,16 @@
       <c r="H17" s="9"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
     </row>
     <row r="19" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
@@ -19173,17 +19183,17 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="1.1437499999999998" bottom="1.1437499999999998" header="0.75" footer="0.75"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -19203,30 +19213,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -19273,10 +19283,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -19299,8 +19309,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -19321,16 +19331,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -19441,16 +19451,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
@@ -19531,16 +19541,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -20615,30 +20625,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -20685,10 +20695,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -20711,8 +20721,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -20733,16 +20743,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -20845,16 +20855,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -20927,16 +20937,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -22007,30 +22017,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -22077,10 +22087,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -22103,8 +22113,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -22125,16 +22135,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
@@ -22249,16 +22259,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
@@ -22334,16 +22344,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -23414,30 +23424,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -23484,10 +23494,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -23510,8 +23520,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -23532,16 +23542,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -23644,16 +23654,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -23726,16 +23736,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -24806,30 +24816,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -24876,10 +24886,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -24902,8 +24912,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -24924,16 +24934,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -25036,16 +25046,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -25118,16 +25128,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
@@ -26198,30 +26208,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="28"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
@@ -26268,10 +26278,10 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -26294,8 +26304,8 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="219" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
@@ -26316,16 +26326,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
     </row>
     <row r="9" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
@@ -26428,16 +26438,16 @@
       <c r="H18" s="9"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6"/>
@@ -26510,16 +26520,16 @@
       <c r="H26" s="9"/>
     </row>
     <row r="27" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
     </row>
     <row r="28" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
